--- a/exports/trm-map-projects-comparables.xlsx
+++ b/exports/trm-map-projects-comparables.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -811,8 +811,16 @@
           <t>00a420908c8249778e11c7d2259afb18</t>
         </is>
       </c>
-      <c r="O8" s="9" t="n"/>
-      <c r="P8" s="9" t="n"/>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>THE LINQ @ BEAUTY WORLD</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>Similar number of units, projects right next to each other</t>
+        </is>
+      </c>
       <c r="Q8" s="10" t="n"/>
     </row>
     <row r="9">
@@ -1018,8 +1026,16 @@
           <t>f8b877eb3d354bdfa56ef5b1b60924ca</t>
         </is>
       </c>
-      <c r="O11" s="9" t="n"/>
-      <c r="P11" s="9" t="n"/>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>ONE MEYER</t>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>Most recent new launch and similar location, but has 10 profitable : 1 unprofitable</t>
+        </is>
+      </c>
       <c r="Q11" s="10" t="n"/>
     </row>
     <row r="12">
@@ -1295,8 +1311,16 @@
           <t>d628a74456874b778432799fd9e53517</t>
         </is>
       </c>
-      <c r="O15" s="9" t="n"/>
-      <c r="P15" s="9" t="n"/>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>SCENECA RESIDENCE</t>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t>Sceneca is the closest new launch in scale and profitability</t>
+        </is>
+      </c>
       <c r="Q15" s="10" t="n"/>
     </row>
     <row r="16">
@@ -1362,8 +1386,16 @@
           <t>0855eefe285a456783eeda789a0203cf</t>
         </is>
       </c>
-      <c r="O16" s="9" t="n"/>
-      <c r="P16" s="9" t="n"/>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>SCENECA RESIDENCE</t>
+        </is>
+      </c>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Similar number of units, both nearby Tanah Merah MRT </t>
+        </is>
+      </c>
       <c r="Q16" s="10" t="n"/>
     </row>
     <row r="17">
@@ -1500,8 +1532,16 @@
           <t>2546baa1d7364ff1b2024aa98c49a248</t>
         </is>
       </c>
-      <c r="O18" s="9" t="n"/>
-      <c r="P18" s="9" t="n"/>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>COMMONWEALTH TOWERS</t>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t>Closest recent new launch in terms of location and size</t>
+        </is>
+      </c>
       <c r="Q18" s="10" t="n"/>
     </row>
     <row r="19">
@@ -1569,8 +1609,16 @@
           <t>697564dce09a4511a8d56e739ecdaabd</t>
         </is>
       </c>
-      <c r="O19" s="9" t="n"/>
-      <c r="P19" s="9" t="n"/>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>WATERGARDENS @ CANBERRA</t>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>Similar location and scale</t>
+        </is>
+      </c>
       <c r="Q19" s="10" t="n"/>
     </row>
     <row r="20">
@@ -1638,8 +1686,16 @@
           <t>227b5a5863fa4631875adcfb07b38cae</t>
         </is>
       </c>
-      <c r="O20" s="9" t="n"/>
-      <c r="P20" s="9" t="n"/>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>THE IMPERIAL</t>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>Old condo (2006) but fully profitable at 100+ transactions</t>
+        </is>
+      </c>
       <c r="Q20" s="10" t="n"/>
     </row>
     <row r="21">
@@ -1844,8 +1900,16 @@
           <t>a8dc1c7b80914f65a5c07128aaa9e777</t>
         </is>
       </c>
-      <c r="O23" s="9" t="n"/>
-      <c r="P23" s="9" t="n"/>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t>THE ESTUARY</t>
+        </is>
+      </c>
+      <c r="P23" s="9" t="inlineStr">
+        <is>
+          <t>Old condo (2008) but very nearby and fully profitable at 123 transactions</t>
+        </is>
+      </c>
       <c r="Q23" s="10" t="n"/>
     </row>
     <row r="24">
@@ -1913,8 +1977,16 @@
           <t>eccc7150c2254954a2371b9655eb459c</t>
         </is>
       </c>
-      <c r="O24" s="9" t="n"/>
-      <c r="P24" s="9" t="n"/>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t>THE SCALA</t>
+        </is>
+      </c>
+      <c r="P24" s="9" t="inlineStr">
+        <is>
+          <t>Quite an old condo (2013) but fully profitable and the newest in the area</t>
+        </is>
+      </c>
       <c r="Q24" s="10" t="n"/>
     </row>
     <row r="25">
@@ -2049,8 +2121,16 @@
           <t>679021ecbcab48be90b64e16e77b82b7</t>
         </is>
       </c>
-      <c r="O26" s="9" t="n"/>
-      <c r="P26" s="9" t="n"/>
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t>TWIN FOUNTAINS</t>
+        </is>
+      </c>
+      <c r="P26" s="9" t="inlineStr">
+        <is>
+          <t>Close to Clovelle of Woodlands and fully profitable at 179 transactions</t>
+        </is>
+      </c>
       <c r="Q26" s="10" t="n"/>
     </row>
     <row r="27">
@@ -2118,8 +2198,16 @@
           <t>60dab94999134e819496275b30b239aa</t>
         </is>
       </c>
-      <c r="O27" s="9" t="n"/>
-      <c r="P27" s="9" t="n"/>
+      <c r="O27" s="9" t="inlineStr">
+        <is>
+          <t>PASIR RIS 8 or RIPPLE BAY</t>
+        </is>
+      </c>
+      <c r="P27" s="9" t="inlineStr">
+        <is>
+          <t>Pasir Ris 8 - Most recent new launch Ripple Bay - Closer in terms of similar location</t>
+        </is>
+      </c>
       <c r="Q27" s="10" t="n"/>
     </row>
     <row r="28">
@@ -2323,8 +2411,16 @@
           <t>cf6fa6bd96944f56ae7ea4d8bdb162cd</t>
         </is>
       </c>
-      <c r="O30" s="9" t="n"/>
-      <c r="P30" s="9" t="n"/>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t>DAIRY FARM RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P30" s="9" t="inlineStr">
+        <is>
+          <t>Similar location, profitable ot unprofitable 67:3</t>
+        </is>
+      </c>
       <c r="Q30" s="10" t="n"/>
     </row>
     <row r="31">
@@ -2531,8 +2627,16 @@
           <t>88a853a0ae6443749b7e5f957b8e6480</t>
         </is>
       </c>
-      <c r="O33" s="9" t="n"/>
-      <c r="P33" s="9" t="n"/>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>THE CLEMENT CANOPY</t>
+        </is>
+      </c>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t>Same district and similar area with similar scale, full positive transactions</t>
+        </is>
+      </c>
       <c r="Q33" s="10" t="n"/>
     </row>
     <row r="34">
@@ -2600,8 +2704,16 @@
           <t>946c32a7bc3c43f6b1df4513a33d371e</t>
         </is>
       </c>
-      <c r="O34" s="9" t="n"/>
-      <c r="P34" s="9" t="n"/>
+      <c r="O34" s="9" t="inlineStr">
+        <is>
+          <t>THE CLEMENT CANOPY</t>
+        </is>
+      </c>
+      <c r="P34" s="9" t="inlineStr">
+        <is>
+          <t>Same district and similar area with similar scale, full positive transactions</t>
+        </is>
+      </c>
       <c r="Q34" s="10" t="n"/>
     </row>
     <row r="35">
@@ -2669,8 +2781,16 @@
           <t>3c4e53308b2c48d0bca49a3984e36eaa</t>
         </is>
       </c>
-      <c r="O35" s="9" t="n"/>
-      <c r="P35" s="9" t="n"/>
+      <c r="O35" s="9" t="inlineStr">
+        <is>
+          <t>THE RESERVE RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P35" s="9" t="inlineStr">
+        <is>
+          <t>Similar area</t>
+        </is>
+      </c>
       <c r="Q35" s="10" t="n"/>
     </row>
     <row r="36">
@@ -2951,8 +3071,16 @@
           <t>1430cfcb8f9c4302860203c0f370a169</t>
         </is>
       </c>
-      <c r="O39" s="9" t="n"/>
-      <c r="P39" s="9" t="n"/>
+      <c r="O39" s="9" t="inlineStr">
+        <is>
+          <t>LIV @ MB</t>
+        </is>
+      </c>
+      <c r="P39" s="9" t="inlineStr">
+        <is>
+          <t>Fully profitable and similar location</t>
+        </is>
+      </c>
       <c r="Q39" s="10" t="n"/>
     </row>
     <row r="40">
@@ -3156,8 +3284,16 @@
           <t>7fc6731e8e4a4121a433521c68998c0c</t>
         </is>
       </c>
-      <c r="O42" s="9" t="n"/>
-      <c r="P42" s="9" t="n"/>
+      <c r="O42" s="9" t="inlineStr">
+        <is>
+          <t>RIVERFRONT RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P42" s="9" t="inlineStr">
+        <is>
+          <t>Fully profitable at 500+ transactions, in Hougang area too</t>
+        </is>
+      </c>
       <c r="Q42" s="10" t="n"/>
     </row>
     <row r="43">
@@ -3225,8 +3361,16 @@
           <t>e80c8fc512304bd7b7969fcf96b00048</t>
         </is>
       </c>
-      <c r="O43" s="9" t="n"/>
-      <c r="P43" s="9" t="n"/>
+      <c r="O43" s="9" t="inlineStr">
+        <is>
+          <t>COMMONWEALTH TOWERS</t>
+        </is>
+      </c>
+      <c r="P43" s="9" t="inlineStr">
+        <is>
+          <t>Closest recent new launch in terms of location and size</t>
+        </is>
+      </c>
       <c r="Q43" s="10" t="n"/>
     </row>
     <row r="44">
@@ -3294,8 +3438,16 @@
           <t>b43a59ee25424f54adb7ea7639a7aee5</t>
         </is>
       </c>
-      <c r="O44" s="9" t="n"/>
-      <c r="P44" s="9" t="n"/>
+      <c r="O44" s="9" t="inlineStr">
+        <is>
+          <t>J Gateway</t>
+        </is>
+      </c>
+      <c r="P44" s="9" t="inlineStr">
+        <is>
+          <t>Similar location, 150:1 profitable to unprofitable</t>
+        </is>
+      </c>
       <c r="Q44" s="10" t="n"/>
     </row>
     <row r="45">
@@ -3432,8 +3584,16 @@
           <t>ad0b6595310b4a0e9bcf1811adab01d1</t>
         </is>
       </c>
-      <c r="O46" s="9" t="n"/>
-      <c r="P46" s="9" t="n"/>
+      <c r="O46" s="9" t="inlineStr">
+        <is>
+          <t>PARC KOMO</t>
+        </is>
+      </c>
+      <c r="P46" s="9" t="inlineStr">
+        <is>
+          <t>Similar location &amp; size, and fully profitable at 43 transactions</t>
+        </is>
+      </c>
       <c r="Q46" s="10" t="n"/>
     </row>
     <row r="47">
@@ -3639,8 +3799,16 @@
           <t>02a030d8f3ca4ed1b2093e94e3b31115</t>
         </is>
       </c>
-      <c r="O49" s="9" t="n"/>
-      <c r="P49" s="9" t="n"/>
+      <c r="O49" s="9" t="inlineStr">
+        <is>
+          <t>LENTOR MODERN</t>
+        </is>
+      </c>
+      <c r="P49" s="9" t="inlineStr">
+        <is>
+          <t>Same location, 61:1 profitable to unprofitable</t>
+        </is>
+      </c>
       <c r="Q49" s="10" t="n"/>
     </row>
     <row r="50">
@@ -3708,8 +3876,16 @@
           <t>e0d7efea415743a79d08cda8de572c09</t>
         </is>
       </c>
-      <c r="O50" s="9" t="n"/>
-      <c r="P50" s="9" t="n"/>
+      <c r="O50" s="9" t="inlineStr">
+        <is>
+          <t>LENTOR MODERN</t>
+        </is>
+      </c>
+      <c r="P50" s="9" t="inlineStr">
+        <is>
+          <t>Same location, 61:1 profitable to unprofitable</t>
+        </is>
+      </c>
       <c r="Q50" s="10" t="n"/>
     </row>
     <row r="51">
@@ -3777,8 +3953,16 @@
           <t>adf9b59f73ba40cc85938836a28d4037</t>
         </is>
       </c>
-      <c r="O51" s="9" t="n"/>
-      <c r="P51" s="9" t="n"/>
+      <c r="O51" s="9" t="inlineStr">
+        <is>
+          <t>LAKE GRANDE</t>
+        </is>
+      </c>
+      <c r="P51" s="9" t="inlineStr">
+        <is>
+          <t>Fully profitable and similar location with the same views</t>
+        </is>
+      </c>
       <c r="Q51" s="10" t="n"/>
     </row>
     <row r="52">
@@ -3846,8 +4030,16 @@
           <t>83b9b826f1f0445ca23b38813aea6358</t>
         </is>
       </c>
-      <c r="O52" s="9" t="n"/>
-      <c r="P52" s="9" t="n"/>
+      <c r="O52" s="9" t="inlineStr">
+        <is>
+          <t>AMBER PARK</t>
+        </is>
+      </c>
+      <c r="P52" s="9" t="inlineStr">
+        <is>
+          <t>Similar location, fully profitable at 87 transactions</t>
+        </is>
+      </c>
       <c r="Q52" s="10" t="n"/>
     </row>
     <row r="53">
@@ -3913,8 +4105,16 @@
           <t>b83a142f417049e58c49b5be22ab0cea</t>
         </is>
       </c>
-      <c r="O53" s="9" t="n"/>
-      <c r="P53" s="9" t="n"/>
+      <c r="O53" s="9" t="inlineStr">
+        <is>
+          <t>THE CRITERION</t>
+        </is>
+      </c>
+      <c r="P53" s="9" t="inlineStr">
+        <is>
+          <t>Similar location, and also fully profitable at 240+ transactions</t>
+        </is>
+      </c>
       <c r="Q53" s="10" t="n"/>
     </row>
     <row r="54">
@@ -3989,8 +4189,16 @@
           <t>030fee210b074a86a512f1f6cfaf62b6</t>
         </is>
       </c>
-      <c r="O54" s="9" t="n"/>
-      <c r="P54" s="9" t="n"/>
+      <c r="O54" s="9" t="inlineStr">
+        <is>
+          <t>THE RESERVE RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P54" s="9" t="inlineStr">
+        <is>
+          <t>Similar location and scale</t>
+        </is>
+      </c>
       <c r="Q54" s="10" t="n"/>
     </row>
     <row r="55">
@@ -4059,8 +4267,16 @@
           <t>4a25b483869c44f38fad81c15c945c4f</t>
         </is>
       </c>
-      <c r="O55" s="9" t="n"/>
-      <c r="P55" s="9" t="n"/>
+      <c r="O55" s="9" t="inlineStr">
+        <is>
+          <t>THE RESERVE RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P55" s="9" t="inlineStr">
+        <is>
+          <t>Similar location and scale</t>
+        </is>
+      </c>
       <c r="Q55" s="10" t="n"/>
     </row>
     <row r="56">
@@ -4197,8 +4413,16 @@
           <t>e2f59c122d1b47af8d9a734fc79fa467</t>
         </is>
       </c>
-      <c r="O57" s="9" t="n"/>
-      <c r="P57" s="9" t="n"/>
+      <c r="O57" s="9" t="inlineStr">
+        <is>
+          <t>SYMPHONY SUITES</t>
+        </is>
+      </c>
+      <c r="P57" s="9" t="inlineStr">
+        <is>
+          <t>Similar location, fully profitable at 244 transactions</t>
+        </is>
+      </c>
       <c r="Q57" s="10" t="n"/>
     </row>
     <row r="58">
@@ -4266,8 +4490,16 @@
           <t>3afb1fde3a244b79bc85e5f39d888ab4</t>
         </is>
       </c>
-      <c r="O58" s="9" t="n"/>
-      <c r="P58" s="9" t="n"/>
+      <c r="O58" s="9" t="inlineStr">
+        <is>
+          <t>PARC ROSEWOOD</t>
+        </is>
+      </c>
+      <c r="P58" s="9" t="inlineStr">
+        <is>
+          <t>Similar location, and best profit ratio at 210:5 profitable to unprofitable transactions</t>
+        </is>
+      </c>
       <c r="Q58" s="10" t="n"/>
     </row>
     <row r="59">
@@ -4402,8 +4634,16 @@
           <t>f12c41ea74b5463a91ff0c84f7481218</t>
         </is>
       </c>
-      <c r="O60" s="9" t="n"/>
-      <c r="P60" s="9" t="n"/>
+      <c r="O60" s="9" t="inlineStr">
+        <is>
+          <t>THE SCALA</t>
+        </is>
+      </c>
+      <c r="P60" s="9" t="inlineStr">
+        <is>
+          <t>Quite an old condo (2013) but fully profitable and the newest in the area</t>
+        </is>
+      </c>
       <c r="Q60" s="10" t="n"/>
     </row>
     <row r="61">
@@ -4472,8 +4712,16 @@
           <t>b1d78cceab4d4515a1ec7969ccda74b8</t>
         </is>
       </c>
-      <c r="O61" s="9" t="n"/>
-      <c r="P61" s="9" t="n"/>
+      <c r="O61" s="9" t="inlineStr">
+        <is>
+          <t>THE SAIL @ MARINA BAY</t>
+        </is>
+      </c>
+      <c r="P61" s="9" t="inlineStr">
+        <is>
+          <t>Similar location, best profit ratio nearby at 229:17 profitable to unprofitable</t>
+        </is>
+      </c>
       <c r="Q61" s="10" t="n"/>
     </row>
     <row r="62">
@@ -4612,8 +4860,16 @@
           <t>af5940a962684cb1ac366e1535d1b7a0</t>
         </is>
       </c>
-      <c r="O63" s="9" t="n"/>
-      <c r="P63" s="9" t="n"/>
+      <c r="O63" s="9" t="inlineStr">
+        <is>
+          <t>TREASURE AT TAMPINES</t>
+        </is>
+      </c>
+      <c r="P63" s="9" t="inlineStr">
+        <is>
+          <t>both mega developments, also at D18</t>
+        </is>
+      </c>
       <c r="Q63" s="10" t="n"/>
     </row>
     <row r="64">
@@ -4683,8 +4939,16 @@
           <t>31378b5622d24478bc68a07ddc399c65</t>
         </is>
       </c>
-      <c r="O64" s="9" t="n"/>
-      <c r="P64" s="9" t="n"/>
+      <c r="O64" s="9" t="inlineStr">
+        <is>
+          <t>STIRLING RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P64" s="9" t="inlineStr">
+        <is>
+          <t>Extremely high profitability ratio</t>
+        </is>
+      </c>
       <c r="Q64" s="10" t="n"/>
     </row>
     <row r="65">
@@ -4752,8 +5016,16 @@
           <t>eaf892dde8d345e7b8beea79e9851184</t>
         </is>
       </c>
-      <c r="O65" s="9" t="n"/>
-      <c r="P65" s="9" t="n"/>
+      <c r="O65" s="9" t="inlineStr">
+        <is>
+          <t>PARC CENTRAL RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P65" s="9" t="inlineStr">
+        <is>
+          <t>At Tampines West too, all profitable</t>
+        </is>
+      </c>
       <c r="Q65" s="10" t="n"/>
     </row>
     <row r="66">
@@ -4821,8 +5093,16 @@
           <t>1917872113dc425797ca4239311a6ee3</t>
         </is>
       </c>
-      <c r="O66" s="9" t="n"/>
-      <c r="P66" s="9" t="n"/>
+      <c r="O66" s="9" t="inlineStr">
+        <is>
+          <t>IRWELL HILL RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P66" s="9" t="inlineStr">
+        <is>
+          <t>Similar location and new, good profitability ratio at 42:3 profitable to unprofitable</t>
+        </is>
+      </c>
       <c r="Q66" s="10" t="n"/>
     </row>
     <row r="67">
@@ -5026,8 +5306,16 @@
           <t>f62ad7ec239241fa8a8bd10dacaf8291</t>
         </is>
       </c>
-      <c r="O69" s="9" t="n"/>
-      <c r="P69" s="9" t="n"/>
+      <c r="O69" s="9" t="inlineStr">
+        <is>
+          <t>WATERGARDENS @ CANBERRA</t>
+        </is>
+      </c>
+      <c r="P69" s="9" t="inlineStr">
+        <is>
+          <t>Similar location and scale</t>
+        </is>
+      </c>
       <c r="Q69" s="10" t="n"/>
     </row>
     <row r="70">
@@ -5298,8 +5586,16 @@
           <t>478f87cc6ca64393bc3aea90f798f484</t>
         </is>
       </c>
-      <c r="O73" s="9" t="n"/>
-      <c r="P73" s="9" t="n"/>
+      <c r="O73" s="9" t="inlineStr">
+        <is>
+          <t>CHESTERVALE</t>
+        </is>
+      </c>
+      <c r="P73" s="9" t="inlineStr">
+        <is>
+          <t>Super old condo (1999) but was also an EC and fully profitable at 51 transactions.</t>
+        </is>
+      </c>
       <c r="Q73" s="10" t="n"/>
     </row>
     <row r="74">
@@ -5505,8 +5801,16 @@
           <t>5862d7b906c54440828e1269d19bf2fc</t>
         </is>
       </c>
-      <c r="O76" s="9" t="n"/>
-      <c r="P76" s="9" t="n"/>
+      <c r="O76" s="9" t="inlineStr">
+        <is>
+          <t>LAKE GRANDE</t>
+        </is>
+      </c>
+      <c r="P76" s="9" t="inlineStr">
+        <is>
+          <t>Similar location and views</t>
+        </is>
+      </c>
       <c r="Q76" s="10" t="n"/>
     </row>
     <row r="77">
@@ -5644,8 +5948,16 @@
           <t>997843e71ffa45d08e3f20e2a0fd96ed</t>
         </is>
       </c>
-      <c r="O78" s="9" t="n"/>
-      <c r="P78" s="9" t="n"/>
+      <c r="O78" s="9" t="inlineStr">
+        <is>
+          <t>LENTOR MODERN</t>
+        </is>
+      </c>
+      <c r="P78" s="9" t="inlineStr">
+        <is>
+          <t>Closeby in location, 61:1 profitable to unprofitable</t>
+        </is>
+      </c>
       <c r="Q78" s="10" t="n"/>
     </row>
     <row r="79">
@@ -5713,8 +6025,16 @@
           <t>655c7d587a7943a2b95bed4d0b4bf182</t>
         </is>
       </c>
-      <c r="O79" s="9" t="n"/>
-      <c r="P79" s="9" t="n"/>
+      <c r="O79" s="9" t="inlineStr">
+        <is>
+          <t>KENT RIDGE HILL RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P79" s="9" t="inlineStr">
+        <is>
+          <t>Closeby in location, fully profitable at 106 transactions.</t>
+        </is>
+      </c>
       <c r="Q79" s="10" t="n"/>
     </row>
     <row r="80">
@@ -5782,8 +6102,16 @@
           <t>81f063c801ef487f8a695b825e20c30c</t>
         </is>
       </c>
-      <c r="O80" s="9" t="n"/>
-      <c r="P80" s="9" t="n"/>
+      <c r="O80" s="9" t="inlineStr">
+        <is>
+          <t>EIGHT RIVERSUITES</t>
+        </is>
+      </c>
+      <c r="P80" s="9" t="inlineStr">
+        <is>
+          <t>same location, 259:1 profitable to unprofitable</t>
+        </is>
+      </c>
       <c r="Q80" s="10" t="n"/>
     </row>
     <row r="81">
@@ -6123,8 +6451,16 @@
           <t>29c864ff55404605890dfbee32692362</t>
         </is>
       </c>
-      <c r="O85" s="9" t="n"/>
-      <c r="P85" s="9" t="n"/>
+      <c r="O85" s="9" t="inlineStr">
+        <is>
+          <t>DAIRY FARM RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P85" s="9" t="inlineStr">
+        <is>
+          <t>Similar location, profitable ot unprofitable 67:3</t>
+        </is>
+      </c>
       <c r="Q85" s="10" t="n"/>
     </row>
     <row r="86">
@@ -6193,8 +6529,16 @@
           <t>23a0bd1f430c4d55a8bf6fd39fb177b8</t>
         </is>
       </c>
-      <c r="O86" s="9" t="n"/>
-      <c r="P86" s="9" t="n"/>
+      <c r="O86" s="9" t="inlineStr">
+        <is>
+          <t>GEM RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P86" s="9" t="inlineStr">
+        <is>
+          <t>Close location and new, with high profitability ratio of 186:1 of profitable to unprofitable</t>
+        </is>
+      </c>
       <c r="Q86" s="10" t="n"/>
     </row>
     <row r="87">
@@ -6469,8 +6813,16 @@
           <t>70b9d30f47f5447da1d5c4252439fd26</t>
         </is>
       </c>
-      <c r="O90" s="9" t="n"/>
-      <c r="P90" s="9" t="n"/>
+      <c r="O90" s="9" t="inlineStr">
+        <is>
+          <t>THE RESERVE RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P90" s="9" t="inlineStr">
+        <is>
+          <t>Similar location</t>
+        </is>
+      </c>
       <c r="Q90" s="10" t="n"/>
     </row>
     <row r="91">
@@ -6676,7 +7028,11 @@
           <t>50ba3d549264456cbe67a97565d66d79</t>
         </is>
       </c>
-      <c r="O93" s="9" t="n"/>
+      <c r="O93" s="9" t="inlineStr">
+        <is>
+          <t>JADESCAPE</t>
+        </is>
+      </c>
       <c r="P93" s="9" t="n"/>
       <c r="Q93" s="10" t="n"/>
     </row>
@@ -6745,8 +7101,16 @@
           <t>54aec0cc3a7a4a058e10fe7e21a44c17</t>
         </is>
       </c>
-      <c r="O94" s="9" t="n"/>
-      <c r="P94" s="9" t="n"/>
+      <c r="O94" s="9" t="inlineStr">
+        <is>
+          <t>ICON</t>
+        </is>
+      </c>
+      <c r="P94" s="9" t="inlineStr">
+        <is>
+          <t>Old condo (2007) but the best profitability ratio of 126:3 profitable to unprofitable in the area</t>
+        </is>
+      </c>
       <c r="Q94" s="10" t="n"/>
     </row>
     <row r="95">
@@ -6815,8 +7179,16 @@
           <t>8799614909f948d280ad127a9f14360a</t>
         </is>
       </c>
-      <c r="O95" s="9" t="n"/>
-      <c r="P95" s="9" t="n"/>
+      <c r="O95" s="9" t="inlineStr">
+        <is>
+          <t>ONE PEARL BANK</t>
+        </is>
+      </c>
+      <c r="P95" s="9" t="inlineStr">
+        <is>
+          <t>Very recent condo but profitable to unprofitable ratio is 53:11</t>
+        </is>
+      </c>
       <c r="Q95" s="10" t="n"/>
     </row>
     <row r="96">
@@ -6953,8 +7325,16 @@
           <t>cf7d4684ea39448697222b2a7d7aeab6</t>
         </is>
       </c>
-      <c r="O97" s="9" t="n"/>
-      <c r="P97" s="9" t="n"/>
+      <c r="O97" s="9" t="inlineStr">
+        <is>
+          <t>COSTA DEL SOL</t>
+        </is>
+      </c>
+      <c r="P97" s="9" t="inlineStr">
+        <is>
+          <t>Very old condo (2004) but fully profitable and same location</t>
+        </is>
+      </c>
       <c r="Q97" s="10" t="n"/>
     </row>
     <row r="98">
@@ -7298,8 +7678,16 @@
           <t>adbd4a81ec6c4032b0c6d018860067f8</t>
         </is>
       </c>
-      <c r="O102" s="9" t="n"/>
-      <c r="P102" s="9" t="n"/>
+      <c r="O102" s="9" t="inlineStr">
+        <is>
+          <t>BELLEWOODS</t>
+        </is>
+      </c>
+      <c r="P102" s="9" t="inlineStr">
+        <is>
+          <t>Similar location and both are ECs, and high profitablity ratio of 213:1 profitable to unprofitable</t>
+        </is>
+      </c>
       <c r="Q102" s="10" t="n"/>
     </row>
     <row r="103">
@@ -7367,11 +7755,18 @@
           <t>a92578afb30f481ea19b4bf48fffb96b</t>
         </is>
       </c>
-      <c r="O103" s="9" t="n"/>
-      <c r="P103" s="9" t="n"/>
+      <c r="O103" s="9" t="inlineStr">
+        <is>
+          <t>IRWELL HILL RESIDENCES</t>
+        </is>
+      </c>
+      <c r="P103" s="9" t="inlineStr">
+        <is>
+          <t>Similar location and new, good profitability ratio at 42:3 profitable to unprofitable</t>
+        </is>
+      </c>
       <c r="Q103" s="10" t="n"/>
     </row>
-    <row r="104"/>
   </sheetData>
   <autoFilter ref="A5:Q103"/>
   <mergeCells count="1">
@@ -7407,7 +7802,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -7485,7 +7879,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
